--- a/Result/profitability/2022.xlsx
+++ b/Result/profitability/2022.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.32</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.04500000000000001</v>
+        <v>-0.03125000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>8.3775</v>
+        <v>9.25625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.77</v>
       </c>
       <c r="M3" t="n">
-        <v>0.075</v>
+        <v>0.11125</v>
       </c>
       <c r="N3" t="n">
-        <v>11.01</v>
+        <v>10.48375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.31</v>
       </c>
       <c r="M4" t="n">
-        <v>0.16</v>
+        <v>0.15125</v>
       </c>
       <c r="N4" t="n">
-        <v>11.615</v>
+        <v>11.12625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.75</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0575</v>
+        <v>-0.065</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.283750000000001</v>
+        <v>-1.813750000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-1.11</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.19375</v>
+        <v>-0.20875</v>
       </c>
       <c r="N6" t="n">
-        <v>-7.233750000000001</v>
+        <v>-7.648750000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.98</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.32125</v>
+        <v>-0.32625</v>
       </c>
       <c r="N7" t="n">
-        <v>-12.56625</v>
+        <v>-12.5575</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.14</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.29875</v>
+        <v>-0.2975</v>
       </c>
       <c r="N8" t="n">
-        <v>-11.74375</v>
+        <v>-11.62625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>-0.23875</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9812500000000003</v>
+        <v>-0.9812500000000021</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2760</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2559</v>
+      </c>
+      <c r="E75" t="n">
+        <v>201</v>
+      </c>
+      <c r="F75" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-20</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-0.74%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-22</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-28</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.09500000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>8.234999999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.009999999999999995</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.111111111111111</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.9400000000000004</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1482649842271293</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.239999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.3680555555555555</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
